--- a/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/06.0_StructureDefinition-Observation-results-laboratory-uv-ips_to_SDTM_LB_generic_domain.xlsx
+++ b/input/attachments/ig-assets/IPS_FHIR_to_CDISC_SDTM/06.0_StructureDefinition-Observation-results-laboratory-uv-ips_to_SDTM_LB_generic_domain.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28507"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29406"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://cdisc-my.sharepoint.com/personal/rbaker_cdisc_org/Documents/1 Real World Data - RWD/1_XSHARE/Spreadsheets for project/IPS FHIR 1.1.0 to SDTMIG 3.4_2024-Nov/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="363" documentId="8_{CF1D40F4-8F31-4827-8E70-6E50CD80F2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4635C5A2-8D39-4B98-9F89-2243147A4C7C}"/>
+  <xr:revisionPtr revIDLastSave="364" documentId="8_{CF1D40F4-8F31-4827-8E70-6E50CD80F2E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E996D51-551B-43DB-8C0E-A521D2094576}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="4" activeTab="4" xr2:uid="{F78289C1-29D8-469E-A6DC-0463B043ABEB}"/>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="8" activeTab="8" xr2:uid="{06D48393-1C63-42A3-80C3-456E0751823E}"/>
@@ -2903,8 +2903,7 @@
     <t xml:space="preserve">CDISC SDTM Study Identifier/STUDYID </t>
   </si>
   <si>
-    <t xml:space="preserve">For each clinical research study, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.
-</t>
+    <t>In case there is no FHIR study ID (ResearchStudy or ResearchDefinition) available for the patient for which the immunization data is mapped, populate the STUDYID variable with a default value "RWDTOSDTM-YYYYMMDD" where the date is the date on which the FHIR dataset was converted to create SDTM datasets.</t>
   </si>
   <si>
     <t xml:space="preserve">Study Identifier/STUDYID is a variable in CDISC Demographics domain that is a unique identifier for a study. STUDYID is used as a key in all CDISC SDTM datasets.
@@ -3239,7 +3238,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -3361,6 +3360,13 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="13">
@@ -3601,7 +3607,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -3874,9 +3880,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -3885,6 +3888,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -24350,7 +24359,7 @@
       <c r="C10" s="62" t="s">
         <v>639</v>
       </c>
-      <c r="D10" s="107" t="s">
+      <c r="D10" s="106" t="s">
         <v>647</v>
       </c>
       <c r="E10" s="66" t="s">
@@ -24414,7 +24423,7 @@
       <c r="D12" s="64" t="s">
         <v>652</v>
       </c>
-      <c r="E12" s="107" t="s">
+      <c r="E12" s="106" t="s">
         <v>653</v>
       </c>
       <c r="F12" s="72" t="s">
@@ -24446,7 +24455,7 @@
       <c r="C13" s="62" t="s">
         <v>639</v>
       </c>
-      <c r="D13" s="108" t="s">
+      <c r="D13" s="107" t="s">
         <v>655</v>
       </c>
       <c r="E13" s="59" t="s">
@@ -24626,7 +24635,7 @@
       <c r="C18" s="62" t="s">
         <v>639</v>
       </c>
-      <c r="D18" s="109" t="s">
+      <c r="D18" s="108" t="s">
         <v>484</v>
       </c>
       <c r="E18" s="59" t="s">
@@ -25168,7 +25177,7 @@
       <c r="C10" s="62" t="s">
         <v>639</v>
       </c>
-      <c r="D10" s="107" t="s">
+      <c r="D10" s="106" t="s">
         <v>647</v>
       </c>
       <c r="E10" s="66" t="s">
@@ -25232,7 +25241,7 @@
       <c r="D12" s="64" t="s">
         <v>652</v>
       </c>
-      <c r="E12" s="107" t="s">
+      <c r="E12" s="106" t="s">
         <v>653</v>
       </c>
       <c r="F12" s="6" t="s">
@@ -25264,7 +25273,7 @@
       <c r="C13" s="62" t="s">
         <v>639</v>
       </c>
-      <c r="D13" s="108" t="s">
+      <c r="D13" s="107" t="s">
         <v>655</v>
       </c>
       <c r="E13" s="59" t="s">
@@ -25444,7 +25453,7 @@
       <c r="C18" s="62" t="s">
         <v>639</v>
       </c>
-      <c r="D18" s="109" t="s">
+      <c r="D18" s="108" t="s">
         <v>484</v>
       </c>
       <c r="E18" s="59" t="s">
@@ -27921,10 +27930,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" s="106" t="s">
+      <c r="A1" s="109" t="s">
         <v>750</v>
       </c>
-      <c r="B1" s="106"/>
+      <c r="B1" s="109"/>
       <c r="C1" s="43"/>
       <c r="D1" s="43"/>
     </row>
@@ -27968,14 +27977,14 @@
         <v>758</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="57.6">
+    <row r="5" spans="1:4" ht="57.75">
       <c r="A5" s="37">
         <v>3</v>
       </c>
       <c r="B5" s="37" t="s">
         <v>759</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="110" t="s">
         <v>760</v>
       </c>
       <c r="D5" s="35" t="s">
@@ -28191,8 +28200,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9c43450b8c34e20acaf1756fc6612395">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0a2045bb9c165ab785731dcc392b30c8" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100699A48AB9E19DA4AB64847A071655FFB" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="fb735b3d8e016bb6466dda22f76823b1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a46baf18-fe18-4a25-9dd7-6596c31699af" xmlns:ns3="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="47d37a05d05a9fe6c5dd27e72eaf287f" ns2:_="" ns3:_="">
     <xsd:import namespace="a46baf18-fe18-4a25-9dd7-6596c31699af"/>
     <xsd:import namespace="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b"/>
     <xsd:element name="properties">
@@ -28215,6 +28224,7 @@
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
                 <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -28282,6 +28292,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="20" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="23" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -28426,6 +28441,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="526f0e77-c4a1-4bb9-a981-799c4b6cfc2b" xsi:nil="true"/>
@@ -28436,23 +28460,14 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9702CD4E-5A7E-499F-B825-A59B988F5940}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F83D8ECB-78A4-4ADF-A1FC-4F61FC4D6E1C}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7EB5645-9C0E-4F7C-AD9C-25A130148FA0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88BA74B-EDB9-44A9-8165-9CC39800CA45}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A88BA74B-EDB9-44A9-8165-9CC39800CA45}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7EB5645-9C0E-4F7C-AD9C-25A130148FA0}"/>
 </file>